--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,23 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>03:48:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12:11:54</t>
         </is>
       </c>
     </row>

--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,193 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19:56:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>19:59:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>66713643_sky</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:11:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20:17:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:19:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20:26:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20:31:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:34:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>66713643_sky</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:34:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>66704151_min</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11:28:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
